--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/4.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/4.xlsx
@@ -426,13 +426,13 @@
         <v>-6.607021310112804</v>
       </c>
       <c r="E2">
-        <v>-13.8520561208163</v>
+        <v>-14.439317687079</v>
       </c>
       <c r="F2">
-        <v>-0.25494926790932</v>
+        <v>-1.501657119735826</v>
       </c>
       <c r="G2">
-        <v>-11.22046085687251</v>
+        <v>-10.4486453592168</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-6.263435824586654</v>
       </c>
       <c r="E3">
-        <v>-14.61423452409928</v>
+        <v>-15.10602680133228</v>
       </c>
       <c r="F3">
-        <v>-0.30393808774348</v>
+        <v>-1.723305870805098</v>
       </c>
       <c r="G3">
-        <v>-11.10581169436395</v>
+        <v>-9.940748355251914</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-5.911229605609087</v>
       </c>
       <c r="E4">
-        <v>-14.87042841260922</v>
+        <v>-16.35012088003754</v>
       </c>
       <c r="F4">
-        <v>-0.2930226904767909</v>
+        <v>-1.202703465902499</v>
       </c>
       <c r="G4">
-        <v>-10.42949943141744</v>
+        <v>-8.367779957977508</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-5.579856448660757</v>
       </c>
       <c r="E5">
-        <v>-15.7542235138422</v>
+        <v>-15.554554037896</v>
       </c>
       <c r="F5">
-        <v>-0.4061809911688145</v>
+        <v>-1.434332387440699</v>
       </c>
       <c r="G5">
-        <v>-10.23608454537441</v>
+        <v>-9.248295763454498</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-5.266410318403801</v>
       </c>
       <c r="E6">
-        <v>-16.04243824206038</v>
+        <v>-17.05409027842592</v>
       </c>
       <c r="F6">
-        <v>-0.076008655026182</v>
+        <v>-1.802180529797459</v>
       </c>
       <c r="G6">
-        <v>-10.10377256721137</v>
+        <v>-9.95885085459537</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-4.982320078258264</v>
       </c>
       <c r="E7">
-        <v>-17.03444122970664</v>
+        <v>-18.05308975841404</v>
       </c>
       <c r="F7">
-        <v>-0.4495882714429114</v>
+        <v>-1.349983048283237</v>
       </c>
       <c r="G7">
-        <v>-9.636953175949165</v>
+        <v>-8.429263487558384</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-4.719401499203483</v>
       </c>
       <c r="E8">
-        <v>-16.24923553609466</v>
+        <v>-17.79106772385622</v>
       </c>
       <c r="F8">
-        <v>-0.2353766029159733</v>
+        <v>-1.116383440693776</v>
       </c>
       <c r="G8">
-        <v>-9.636162401553339</v>
+        <v>-8.144269707791253</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-4.485227008410242</v>
       </c>
       <c r="E9">
-        <v>-18.5416713475756</v>
+        <v>-18.70704668986171</v>
       </c>
       <c r="F9">
-        <v>-0.4214544293416318</v>
+        <v>-1.312244286146497</v>
       </c>
       <c r="G9">
-        <v>-9.802543303168102</v>
+        <v>-8.732435234764838</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-4.268703433196984</v>
       </c>
       <c r="E10">
-        <v>-18.92092198876997</v>
+        <v>-19.33213459951049</v>
       </c>
       <c r="F10">
-        <v>0.03578615292083369</v>
+        <v>-1.201566117458455</v>
       </c>
       <c r="G10">
-        <v>-9.837343939027573</v>
+        <v>-7.828183072526825</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-4.06460226077292</v>
       </c>
       <c r="E11">
-        <v>-18.85251486041011</v>
+        <v>-19.98797537614536</v>
       </c>
       <c r="F11">
-        <v>-0.1634022443889326</v>
+        <v>-1.399099436697428</v>
       </c>
       <c r="G11">
-        <v>-9.604938297193662</v>
+        <v>-8.443782892958927</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-3.864821022906335</v>
       </c>
       <c r="E12">
-        <v>-19.86989994486936</v>
+        <v>-21.25789081364235</v>
       </c>
       <c r="F12">
-        <v>0.1620541961295623</v>
+        <v>-0.8107208392651755</v>
       </c>
       <c r="G12">
-        <v>-8.81786183806498</v>
+        <v>-8.003958111466279</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-3.654105406537877</v>
       </c>
       <c r="E13">
-        <v>-19.82116450759881</v>
+        <v>-21.50147743051494</v>
       </c>
       <c r="F13">
-        <v>0.3951468428685096</v>
+        <v>-1.00106144434564</v>
       </c>
       <c r="G13">
-        <v>-8.643707722575893</v>
+        <v>-9.047567034555467</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-3.431819317115167</v>
       </c>
       <c r="E14">
-        <v>-21.07646655947305</v>
+        <v>-20.51591393290758</v>
       </c>
       <c r="F14">
-        <v>0.3767951914268894</v>
+        <v>-0.5967974425944116</v>
       </c>
       <c r="G14">
-        <v>-8.515067431337863</v>
+        <v>-6.677219142455724</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-3.190052950875637</v>
       </c>
       <c r="E15">
-        <v>-21.91029447850539</v>
+        <v>-21.40230837822096</v>
       </c>
       <c r="F15">
-        <v>0.9433421659583608</v>
+        <v>-0.3310936279420533</v>
       </c>
       <c r="G15">
-        <v>-8.41840920663974</v>
+        <v>-8.199338449223413</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-2.934666326939279</v>
       </c>
       <c r="E16">
-        <v>-22.49475291935735</v>
+        <v>-22.24363997868402</v>
       </c>
       <c r="F16">
-        <v>1.12845245925755</v>
+        <v>-0.102488247424071</v>
       </c>
       <c r="G16">
-        <v>-8.182505782623462</v>
+        <v>-7.632238364661465</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-2.675394316418674</v>
       </c>
       <c r="E17">
-        <v>-22.72811424192062</v>
+        <v>-22.67464654931205</v>
       </c>
       <c r="F17">
-        <v>1.398115870095289</v>
+        <v>1.271407135428271</v>
       </c>
       <c r="G17">
-        <v>-7.69023067450309</v>
+        <v>-7.270257283445083</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-2.421503749547745</v>
       </c>
       <c r="E18">
-        <v>-24.33118498368791</v>
+        <v>-24.40996684599935</v>
       </c>
       <c r="F18">
-        <v>1.860817050277009</v>
+        <v>0.5008349263220874</v>
       </c>
       <c r="G18">
-        <v>-7.142260111632704</v>
+        <v>-6.323969391809024</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-2.192091212379367</v>
       </c>
       <c r="E19">
-        <v>-24.32142612220138</v>
+        <v>-24.624661798703</v>
       </c>
       <c r="F19">
-        <v>1.951768477634784</v>
+        <v>1.026215354404035</v>
       </c>
       <c r="G19">
-        <v>-7.396571188597467</v>
+        <v>-6.896782083105967</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-1.994964765381108</v>
       </c>
       <c r="E20">
-        <v>-25.46165512106671</v>
+        <v>-25.69047438420028</v>
       </c>
       <c r="F20">
-        <v>2.295226170183515</v>
+        <v>1.435611092215606</v>
       </c>
       <c r="G20">
-        <v>-6.494550257019877</v>
+        <v>-6.416358747258309</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-1.841957366752171</v>
       </c>
       <c r="E21">
-        <v>-25.65363071967388</v>
+        <v>-26.1801518640717</v>
       </c>
       <c r="F21">
-        <v>2.726118042097734</v>
+        <v>1.57816980876779</v>
       </c>
       <c r="G21">
-        <v>-7.272787105267415</v>
+        <v>-6.307435316370983</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-1.73751219082882</v>
       </c>
       <c r="E22">
-        <v>-26.66377477419487</v>
+        <v>-25.23910779443376</v>
       </c>
       <c r="F22">
-        <v>3.067799714934862</v>
+        <v>1.577573384237774</v>
       </c>
       <c r="G22">
-        <v>-7.34142369784788</v>
+        <v>-6.200477337197763</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-1.679708765930538</v>
       </c>
       <c r="E23">
-        <v>-27.24516290966962</v>
+        <v>-26.96084266909804</v>
       </c>
       <c r="F23">
-        <v>3.345745143065792</v>
+        <v>2.027749649289166</v>
       </c>
       <c r="G23">
-        <v>-6.293142315258041</v>
+        <v>-6.809583620163724</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-1.668148991029918</v>
       </c>
       <c r="E24">
-        <v>-27.61731743209398</v>
+        <v>-27.92433438439201</v>
       </c>
       <c r="F24">
-        <v>3.543912163367906</v>
+        <v>2.267780701393962</v>
       </c>
       <c r="G24">
-        <v>-6.777791864474263</v>
+        <v>-5.441514384390403</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-1.690824793467459</v>
       </c>
       <c r="E25">
-        <v>-27.43667207545401</v>
+        <v>-28.16442954780468</v>
       </c>
       <c r="F25">
-        <v>3.4792862520711</v>
+        <v>2.46743712628631</v>
       </c>
       <c r="G25">
-        <v>-6.246296315053849</v>
+        <v>-5.764087994677854</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-1.739167612847197</v>
       </c>
       <c r="E26">
-        <v>-27.37785172656837</v>
+        <v>-27.84514495941988</v>
       </c>
       <c r="F26">
-        <v>3.410051304545117</v>
+        <v>2.534322823857953</v>
       </c>
       <c r="G26">
-        <v>-6.633286866996318</v>
+        <v>-6.517718962451116</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-1.798503573531128</v>
       </c>
       <c r="E27">
-        <v>-28.00291699384711</v>
+        <v>-27.79974247901897</v>
       </c>
       <c r="F27">
-        <v>3.334645019868279</v>
+        <v>2.732723443767657</v>
       </c>
       <c r="G27">
-        <v>-7.397821334011615</v>
+        <v>-6.296764783859668</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-1.852899301567688</v>
       </c>
       <c r="E28">
-        <v>-27.52486863522739</v>
+        <v>-27.97124937511148</v>
       </c>
       <c r="F28">
-        <v>3.240839038440457</v>
+        <v>2.251041052918189</v>
       </c>
       <c r="G28">
-        <v>-7.278988614014765</v>
+        <v>-6.555807382313151</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-1.889545451884283</v>
       </c>
       <c r="E29">
-        <v>-28.4268048033351</v>
+        <v>-27.77267126140112</v>
       </c>
       <c r="F29">
-        <v>3.162790261748687</v>
+        <v>2.630681833621203</v>
       </c>
       <c r="G29">
-        <v>-7.044105649903475</v>
+        <v>-7.868663502905695</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-1.893877910345714</v>
       </c>
       <c r="E30">
-        <v>-27.33758000721816</v>
+        <v>-27.58850728045718</v>
       </c>
       <c r="F30">
-        <v>3.213198074943843</v>
+        <v>2.519650780419568</v>
       </c>
       <c r="G30">
-        <v>-7.796233818202512</v>
+        <v>-7.00336600302141</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-1.85957944147269</v>
       </c>
       <c r="E31">
-        <v>-27.91578915393954</v>
+        <v>-28.15831157942032</v>
       </c>
       <c r="F31">
-        <v>2.956276611495965</v>
+        <v>2.457334357441767</v>
       </c>
       <c r="G31">
-        <v>-7.430581050061112</v>
+        <v>-6.949088035985075</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-1.782982681379089</v>
       </c>
       <c r="E32">
-        <v>-27.97320114740878</v>
+        <v>-27.64299840819148</v>
       </c>
       <c r="F32">
-        <v>2.923373858256769</v>
+        <v>2.118414461525572</v>
       </c>
       <c r="G32">
-        <v>-8.459493381785547</v>
+        <v>-6.967121629675783</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-1.666197682895592</v>
       </c>
       <c r="E33">
-        <v>-27.86123009909512</v>
+        <v>-27.90508836985941</v>
       </c>
       <c r="F33">
-        <v>2.881705321161148</v>
+        <v>1.536479734119697</v>
       </c>
       <c r="G33">
-        <v>-7.555766214997046</v>
+        <v>-7.623372504007845</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-1.517507019743024</v>
       </c>
       <c r="E34">
-        <v>-26.67353363568139</v>
+        <v>-26.18296857490447</v>
       </c>
       <c r="F34">
-        <v>2.705175257420156</v>
+        <v>1.860431031067305</v>
       </c>
       <c r="G34">
-        <v>-8.332139329398819</v>
+        <v>-7.747028619697079</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-1.346242999713322</v>
       </c>
       <c r="E35">
-        <v>-27.06170537067088</v>
+        <v>-27.9423939387346</v>
       </c>
       <c r="F35">
-        <v>2.6299710943896</v>
+        <v>1.623302578341918</v>
       </c>
       <c r="G35">
-        <v>-7.709858941871689</v>
+        <v>-7.14228636140518</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-1.166787182182592</v>
       </c>
       <c r="E36">
-        <v>-26.49930512671029</v>
+        <v>-26.39808467569084</v>
       </c>
       <c r="F36">
-        <v>2.612181076047078</v>
+        <v>1.808376423475384</v>
       </c>
       <c r="G36">
-        <v>-7.028720002011239</v>
+        <v>-6.398945304442337</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-0.9912677454478849</v>
       </c>
       <c r="E37">
-        <v>-26.98876523982934</v>
+        <v>-25.71722408016359</v>
       </c>
       <c r="F37">
-        <v>2.250741183918376</v>
+        <v>2.134047411151204</v>
       </c>
       <c r="G37">
-        <v>-7.047826555151885</v>
+        <v>-6.465951129907757</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-0.8305748125662192</v>
       </c>
       <c r="E38">
-        <v>-26.27989150409064</v>
+        <v>-25.99375534544198</v>
       </c>
       <c r="F38">
-        <v>2.409961682410469</v>
+        <v>1.384121431192395</v>
       </c>
       <c r="G38">
-        <v>-7.47384067510083</v>
+        <v>-6.338682389281574</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-0.6937315594704758</v>
       </c>
       <c r="E39">
-        <v>-25.79889510889193</v>
+        <v>-26.27387769060845</v>
       </c>
       <c r="F39">
-        <v>2.466075290276107</v>
+        <v>1.166805870007167</v>
       </c>
       <c r="G39">
-        <v>-6.918756423889568</v>
+        <v>-6.711619469284942</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-0.5841234425406813</v>
       </c>
       <c r="E40">
-        <v>-25.76511269279471</v>
+        <v>-25.56038943985595</v>
       </c>
       <c r="F40">
-        <v>2.060832986622172</v>
+        <v>1.284626222442146</v>
       </c>
       <c r="G40">
-        <v>-6.448157065390888</v>
+        <v>-6.65141561611225</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-0.5058678696795403</v>
       </c>
       <c r="E41">
-        <v>-26.33857599875604</v>
+        <v>-24.40972683687695</v>
       </c>
       <c r="F41">
-        <v>2.153666464719107</v>
+        <v>1.18877417352941</v>
       </c>
       <c r="G41">
-        <v>-5.857271405744524</v>
+        <v>-7.239223489935855</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-0.4568633994161039</v>
       </c>
       <c r="E42">
-        <v>-25.22660920617259</v>
+        <v>-25.5081127359114</v>
       </c>
       <c r="F42">
-        <v>2.19045923128185</v>
+        <v>1.479181560868055</v>
       </c>
       <c r="G42">
-        <v>-5.963727358019148</v>
+        <v>-6.355268964264567</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-0.4345343206913794</v>
       </c>
       <c r="E43">
-        <v>-24.95207046945757</v>
+        <v>-23.48311048542744</v>
       </c>
       <c r="F43">
-        <v>1.816337034216287</v>
+        <v>1.239233345503539</v>
       </c>
       <c r="G43">
-        <v>-5.537814955938546</v>
+        <v>-6.084705996915875</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-0.4353830120777253</v>
       </c>
       <c r="E44">
-        <v>-24.8193137254487</v>
+        <v>-23.76875756888327</v>
       </c>
       <c r="F44">
-        <v>1.846201335822015</v>
+        <v>1.304561712357919</v>
       </c>
       <c r="G44">
-        <v>-5.26325546073045</v>
+        <v>-4.39757405792371</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-0.452611211520588</v>
       </c>
       <c r="E45">
-        <v>-24.42288658234324</v>
+        <v>-24.0676323249155</v>
       </c>
       <c r="F45">
-        <v>1.468222260129017</v>
+        <v>0.9959965115499086</v>
       </c>
       <c r="G45">
-        <v>-5.957529130493358</v>
+        <v>-4.635052468288522</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-0.4836047251244817</v>
       </c>
       <c r="E46">
-        <v>-24.22812597222135</v>
+        <v>-23.96676962334266</v>
       </c>
       <c r="F46">
-        <v>1.565242307079701</v>
+        <v>0.917903003018388</v>
       </c>
       <c r="G46">
-        <v>-5.350572047648833</v>
+        <v>-4.964877578222345</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-0.5231037375621223</v>
       </c>
       <c r="E47">
-        <v>-23.98082600666247</v>
+        <v>-23.83419854676811</v>
       </c>
       <c r="F47">
-        <v>1.218482742063411</v>
+        <v>0.4493949673430436</v>
       </c>
       <c r="G47">
-        <v>-5.243623912140293</v>
+        <v>-4.726805266755274</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-0.5694546912166566</v>
       </c>
       <c r="E48">
-        <v>-23.62295881973231</v>
+        <v>-22.75435674879507</v>
       </c>
       <c r="F48">
-        <v>1.150965828530835</v>
+        <v>0.663651367709733</v>
       </c>
       <c r="G48">
-        <v>-5.406415157369023</v>
+        <v>-4.879273788957992</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-0.6224358999650379</v>
       </c>
       <c r="E49">
-        <v>-23.50594757984812</v>
+        <v>-22.24616686718029</v>
       </c>
       <c r="F49">
-        <v>1.251634005523447</v>
+        <v>0.499130146207126</v>
       </c>
       <c r="G49">
-        <v>-4.621120401547119</v>
+        <v>-5.389956550026849</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-0.6814277240377425</v>
       </c>
       <c r="E50">
-        <v>-22.14795785137595</v>
+        <v>-22.17429092773055</v>
       </c>
       <c r="F50">
-        <v>0.9620003133390169</v>
+        <v>0.5837246821158171</v>
       </c>
       <c r="G50">
-        <v>-5.348632845707201</v>
+        <v>-5.6503608554275</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-0.7500861902646305</v>
       </c>
       <c r="E51">
-        <v>-22.86233368303396</v>
+        <v>-20.74442525980864</v>
       </c>
       <c r="F51">
-        <v>1.141275586652886</v>
+        <v>0.5874299695085392</v>
       </c>
       <c r="G51">
-        <v>-5.431700250706104</v>
+        <v>-4.735979562235482</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-0.8287419043034144</v>
       </c>
       <c r="E52">
-        <v>-21.82574786878219</v>
+        <v>-22.56683264013744</v>
       </c>
       <c r="F52">
-        <v>0.9908639471221629</v>
+        <v>0.5116103294977034</v>
       </c>
       <c r="G52">
-        <v>-5.21267871161317</v>
+        <v>-5.174377012349771</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-0.9210877360975644</v>
       </c>
       <c r="E53">
-        <v>-21.55653461750019</v>
+        <v>-21.89898687890824</v>
       </c>
       <c r="F53">
-        <v>0.7274712775236153</v>
+        <v>0.484714896663609</v>
       </c>
       <c r="G53">
-        <v>-4.88785090211438</v>
+        <v>-4.025230879022602</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-1.029272083089253</v>
       </c>
       <c r="E54">
-        <v>-21.47351410351757</v>
+        <v>-20.21210766868099</v>
       </c>
       <c r="F54">
-        <v>0.668542877223264</v>
+        <v>-0.195296874498922</v>
       </c>
       <c r="G54">
-        <v>-5.000163834872613</v>
+        <v>-4.951431132271741</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-1.15336116126579</v>
       </c>
       <c r="E55">
-        <v>-21.09294114791295</v>
+        <v>-22.08817746600069</v>
       </c>
       <c r="F55">
-        <v>0.2496374816275541</v>
+        <v>0.2173667727166937</v>
       </c>
       <c r="G55">
-        <v>-5.297084855008325</v>
+        <v>-4.778645286172941</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-1.295480934050995</v>
       </c>
       <c r="E56">
-        <v>-20.81600684844788</v>
+        <v>-20.68319576275092</v>
       </c>
       <c r="F56">
-        <v>0.3232810004712357</v>
+        <v>0.2273113233873018</v>
       </c>
       <c r="G56">
-        <v>-5.242961105385285</v>
+        <v>-3.922380989241808</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-1.451571344561704</v>
       </c>
       <c r="E57">
-        <v>-20.60170134450889</v>
+        <v>-21.58966946181431</v>
       </c>
       <c r="F57">
-        <v>0.3109772594374546</v>
+        <v>-0.1298558496777611</v>
       </c>
       <c r="G57">
-        <v>-5.240588782197806</v>
+        <v>-4.765359620078749</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-1.619830753129266</v>
       </c>
       <c r="E58">
-        <v>-19.82699718212069</v>
+        <v>-21.74403608378778</v>
       </c>
       <c r="F58">
-        <v>0.3617918010273847</v>
+        <v>-0.540932344949613</v>
       </c>
       <c r="G58">
-        <v>-4.947037576603644</v>
+        <v>-4.606394279188331</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-1.794435373546515</v>
       </c>
       <c r="E59">
-        <v>-19.96114416764991</v>
+        <v>-18.36070899775508</v>
       </c>
       <c r="F59">
-        <v>0.4612074865069646</v>
+        <v>0.5263411870216869</v>
       </c>
       <c r="G59">
-        <v>-5.477916256370883</v>
+        <v>-4.78615928354407</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-1.96794623744546</v>
       </c>
       <c r="E60">
-        <v>-19.56819489258233</v>
+        <v>-20.76502075959552</v>
       </c>
       <c r="F60">
-        <v>-0.1077053053269023</v>
+        <v>-0.1211778727660334</v>
       </c>
       <c r="G60">
-        <v>-4.790208310948424</v>
+        <v>-4.763955257251308</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-2.135098983503596</v>
       </c>
       <c r="E61">
-        <v>-19.34132740174606</v>
+        <v>-20.40572257487894</v>
       </c>
       <c r="F61">
-        <v>-0.1068065266948648</v>
+        <v>0.2081834916892584</v>
       </c>
       <c r="G61">
-        <v>-5.243597662367817</v>
+        <v>-4.703236252293783</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-2.286469642296329</v>
       </c>
       <c r="E62">
-        <v>-19.94392690947275</v>
+        <v>-19.52498872207515</v>
       </c>
       <c r="F62">
-        <v>0.06909149271779061</v>
+        <v>-0.2376554416410747</v>
       </c>
       <c r="G62">
-        <v>-5.622549221489646</v>
+        <v>-5.268128074746225</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-2.417040631887235</v>
       </c>
       <c r="E63">
-        <v>-19.07346363571835</v>
+        <v>-18.43522956602531</v>
       </c>
       <c r="F63">
-        <v>-0.1109624459547099</v>
+        <v>-0.617524023379858</v>
       </c>
       <c r="G63">
-        <v>-5.870835975671269</v>
+        <v>-5.50659413280043</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-2.519535150015035</v>
       </c>
       <c r="E64">
-        <v>-19.35176100585973</v>
+        <v>-17.92187722404179</v>
       </c>
       <c r="F64">
-        <v>-0.1677188669249209</v>
+        <v>-0.1449205392650729</v>
       </c>
       <c r="G64">
-        <v>-5.629771190141985</v>
+        <v>-5.169960488130759</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-2.587910562915104</v>
       </c>
       <c r="E65">
-        <v>-18.9608450156216</v>
+        <v>-17.46567875250907</v>
       </c>
       <c r="F65">
-        <v>-0.3751105866246107</v>
+        <v>-0.2480829305075149</v>
       </c>
       <c r="G65">
-        <v>-5.335366866942366</v>
+        <v>-6.139538490395756</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-2.61954290942535</v>
       </c>
       <c r="E66">
-        <v>-19.35828200843078</v>
+        <v>-19.30972771012054</v>
       </c>
       <c r="F66">
-        <v>-0.3620729120719492</v>
+        <v>-0.5932230372513317</v>
       </c>
       <c r="G66">
-        <v>-5.829433522034195</v>
+        <v>-6.225398214941746</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-2.610506149849583</v>
       </c>
       <c r="E67">
-        <v>-18.35973084736942</v>
+        <v>-19.61466156437503</v>
       </c>
       <c r="F67">
-        <v>-0.5382749423214321</v>
+        <v>-0.8482425691423819</v>
       </c>
       <c r="G67">
-        <v>-6.648980949715142</v>
+        <v>-7.184768336935311</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-2.562917689903497</v>
       </c>
       <c r="E68">
-        <v>-18.52498844933134</v>
+        <v>-18.18728202868333</v>
       </c>
       <c r="F68">
-        <v>-0.6542803417768777</v>
+        <v>-0.4033811093473522</v>
       </c>
       <c r="G68">
-        <v>-6.541406100888747</v>
+        <v>-5.750316707792864</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-2.478147761404423</v>
       </c>
       <c r="E69">
-        <v>-17.65248283379949</v>
+        <v>-18.34080635449137</v>
       </c>
       <c r="F69">
-        <v>-0.6868078445826058</v>
+        <v>0.0548750513509455</v>
       </c>
       <c r="G69">
-        <v>-6.050981601727902</v>
+        <v>-6.402000121714179</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-2.360733336773326</v>
       </c>
       <c r="E70">
-        <v>-18.55307404512691</v>
+        <v>-18.22243204393087</v>
       </c>
       <c r="F70">
-        <v>-0.6116624956376487</v>
+        <v>-0.9739597480282489</v>
       </c>
       <c r="G70">
-        <v>-5.983956088933125</v>
+        <v>-6.824142400222979</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-2.217770296454195</v>
       </c>
       <c r="E71">
-        <v>-18.32794548830959</v>
+        <v>-17.93213421766916</v>
       </c>
       <c r="F71">
-        <v>-0.8365625887629089</v>
+        <v>-0.6745703729410487</v>
       </c>
       <c r="G71">
-        <v>-6.714854753742554</v>
+        <v>-6.299655540053539</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-2.054274187699714</v>
       </c>
       <c r="E72">
-        <v>-18.55530205433869</v>
+        <v>-17.90847746945309</v>
       </c>
       <c r="F72">
-        <v>-0.9428015365393483</v>
+        <v>-0.7854630887864158</v>
       </c>
       <c r="G72">
-        <v>-6.099763522652167</v>
+        <v>-6.323834861725087</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-1.880094938079357</v>
       </c>
       <c r="E73">
-        <v>-18.06270370873232</v>
+        <v>-18.62266310520278</v>
       </c>
       <c r="F73">
-        <v>-1.050828929538432</v>
+        <v>-1.035839621384775</v>
       </c>
       <c r="G73">
-        <v>-6.241164484534877</v>
+        <v>-6.373899740279095</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-1.701216416370157</v>
       </c>
       <c r="E74">
-        <v>-18.53367406247805</v>
+        <v>-17.46976343606399</v>
       </c>
       <c r="F74">
-        <v>-1.020536361985457</v>
+        <v>-0.652646801258557</v>
       </c>
       <c r="G74">
-        <v>-5.900048691215005</v>
+        <v>-6.354704594156343</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-1.524946040672939</v>
       </c>
       <c r="E75">
-        <v>-18.1547947561523</v>
+        <v>-18.812306539696</v>
       </c>
       <c r="F75">
-        <v>-1.140427632927435</v>
+        <v>-0.5875462354399467</v>
       </c>
       <c r="G75">
-        <v>-6.113593871525226</v>
+        <v>-6.12775234255423</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-1.35857738423357</v>
       </c>
       <c r="E76">
-        <v>-18.54549337963807</v>
+        <v>-18.07684613305827</v>
       </c>
       <c r="F76">
-        <v>-1.229141639930248</v>
+        <v>-1.570638586836552</v>
       </c>
       <c r="G76">
-        <v>-5.670963645599254</v>
+        <v>-6.468320171873676</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-1.205004743841061</v>
       </c>
       <c r="E77">
-        <v>-18.07501210108517</v>
+        <v>-19.56260675565686</v>
       </c>
       <c r="F77">
-        <v>-1.285676886803911</v>
+        <v>-1.210008838027788</v>
       </c>
       <c r="G77">
-        <v>-5.458927827206376</v>
+        <v>-4.865259691677603</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-1.071333144092575</v>
       </c>
       <c r="E78">
-        <v>-19.14802043178063</v>
+        <v>-19.06104655998932</v>
       </c>
       <c r="F78">
-        <v>-1.298059322740958</v>
+        <v>-1.580574853833132</v>
       </c>
       <c r="G78">
-        <v>-5.756856182360838</v>
+        <v>-6.577102510233947</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-0.9586258643574928</v>
       </c>
       <c r="E79">
-        <v>-19.42489586108361</v>
+        <v>-20.80335429207045</v>
       </c>
       <c r="F79">
-        <v>-1.404735648506076</v>
+        <v>-1.462553208119273</v>
       </c>
       <c r="G79">
-        <v>-5.383633636081798</v>
+        <v>-6.113876056579339</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-0.8696489739573303</v>
       </c>
       <c r="E80">
-        <v>-20.21375603321978</v>
+        <v>-20.46889931575995</v>
       </c>
       <c r="F80">
-        <v>-1.440928677069192</v>
+        <v>-1.659258988322849</v>
       </c>
       <c r="G80">
-        <v>-4.765878053085141</v>
+        <v>-6.571104437223282</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-0.8055964071323016</v>
       </c>
       <c r="E81">
-        <v>-20.75948696435815</v>
+        <v>-20.28233977206595</v>
       </c>
       <c r="F81">
-        <v>-1.544718142435553</v>
+        <v>-1.674815728147424</v>
       </c>
       <c r="G81">
-        <v>-4.900099702195787</v>
+        <v>-6.041626839061926</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-0.7638373790741602</v>
       </c>
       <c r="E82">
-        <v>-20.87402112896014</v>
+        <v>-21.38062604467224</v>
       </c>
       <c r="F82">
-        <v>-1.547367261389706</v>
+        <v>-2.252121538506455</v>
       </c>
       <c r="G82">
-        <v>-5.03977802275979</v>
+        <v>-5.179686028832952</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-0.7455094590924743</v>
       </c>
       <c r="E83">
-        <v>-21.20452274746195</v>
+        <v>-23.21300512476593</v>
       </c>
       <c r="F83">
-        <v>-1.576849685622743</v>
+        <v>-1.708051485082545</v>
       </c>
       <c r="G83">
-        <v>-4.881265490444575</v>
+        <v>-5.333450633551651</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-0.7461084954486686</v>
       </c>
       <c r="E84">
-        <v>-22.5029313434152</v>
+        <v>-23.46857861233682</v>
       </c>
       <c r="F84">
-        <v>-1.616984086288379</v>
+        <v>-1.437850463800389</v>
       </c>
       <c r="G84">
-        <v>-4.860387077661827</v>
+        <v>-5.53435982963645</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-0.7633999905461735</v>
       </c>
       <c r="E85">
-        <v>-24.03950144437986</v>
+        <v>-24.32270315187154</v>
       </c>
       <c r="F85">
-        <v>-1.571942437128559</v>
+        <v>-1.509918427843946</v>
       </c>
       <c r="G85">
-        <v>-5.211159506031146</v>
+        <v>-5.118947336546071</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-0.7935662818360607</v>
       </c>
       <c r="E86">
-        <v>-24.19193440795205</v>
+        <v>-25.47178531742187</v>
       </c>
       <c r="F86">
-        <v>-1.781629562901406</v>
+        <v>-1.576182021496087</v>
       </c>
       <c r="G86">
-        <v>-5.303401206510256</v>
+        <v>-5.779030677659565</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-0.831028489822688</v>
       </c>
       <c r="E87">
-        <v>-25.36584619648643</v>
+        <v>-26.93796028993728</v>
       </c>
       <c r="F87">
-        <v>-1.967973295263363</v>
+        <v>-1.786452317920505</v>
       </c>
       <c r="G87">
-        <v>-4.654063866003944</v>
+        <v>-6.169541980335318</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-0.8724281643914515</v>
       </c>
       <c r="E88">
-        <v>-25.80856792937231</v>
+        <v>-28.35405939687588</v>
       </c>
       <c r="F88">
-        <v>-1.911608692074676</v>
+        <v>-1.627293946983622</v>
       </c>
       <c r="G88">
-        <v>-4.983629759434572</v>
+        <v>-5.93872116851462</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-0.911375184333973</v>
       </c>
       <c r="E89">
-        <v>-27.94956704156275</v>
+        <v>-29.38996594002651</v>
       </c>
       <c r="F89">
-        <v>-1.749486422570577</v>
+        <v>-1.832099503651772</v>
       </c>
       <c r="G89">
-        <v>-5.672423789193206</v>
+        <v>-5.804788266901206</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-0.9446085625388344</v>
       </c>
       <c r="E90">
-        <v>-28.95482034415545</v>
+        <v>-30.69926778020521</v>
       </c>
       <c r="F90">
-        <v>-2.007456599150399</v>
+        <v>-2.520476128847772</v>
       </c>
       <c r="G90">
-        <v>-5.681342149391777</v>
+        <v>-5.394304168593113</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-0.9684288103417362</v>
       </c>
       <c r="E91">
-        <v>-30.67949872692472</v>
+        <v>-32.03157879681689</v>
       </c>
       <c r="F91">
-        <v>-1.718468205172749</v>
+        <v>-2.175242416587439</v>
       </c>
       <c r="G91">
-        <v>-5.507532562166431</v>
+        <v>-6.757763288075413</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-0.9796345667823064</v>
       </c>
       <c r="E92">
-        <v>-32.42347293744068</v>
+        <v>-34.47364218222227</v>
       </c>
       <c r="F92">
-        <v>-1.753036805258976</v>
+        <v>-1.756834041433408</v>
       </c>
       <c r="G92">
-        <v>-5.88714036560015</v>
+        <v>-6.534197257122647</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-0.9769702833926518</v>
       </c>
       <c r="E93">
-        <v>-34.08290506670743</v>
+        <v>-34.06583045546152</v>
       </c>
       <c r="F93">
-        <v>-1.919006841349079</v>
+        <v>-2.359656052900873</v>
       </c>
       <c r="G93">
-        <v>-6.456455274714724</v>
+        <v>-6.24499038887319</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-0.9583753017921686</v>
       </c>
       <c r="E94">
-        <v>-35.91157759082585</v>
+        <v>-36.01857184620508</v>
       </c>
       <c r="F94">
-        <v>-1.898360612201704</v>
+        <v>-2.553036766349612</v>
       </c>
       <c r="G94">
-        <v>-6.469383287658935</v>
+        <v>-6.959683100400522</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-0.9240325624019661</v>
       </c>
       <c r="E95">
-        <v>-37.59280979396554</v>
+        <v>-39.24358121669262</v>
       </c>
       <c r="F95">
-        <v>-1.870396585417998</v>
+        <v>-2.506905814055111</v>
       </c>
       <c r="G95">
-        <v>-6.046059769388735</v>
+        <v>-8.153962436277853</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-0.8736920766121699</v>
       </c>
       <c r="E96">
-        <v>-39.4931839112844</v>
+        <v>-41.03820188051036</v>
       </c>
       <c r="F96">
-        <v>-1.702762359215671</v>
+        <v>-2.232018718375317</v>
       </c>
       <c r="G96">
-        <v>-7.494184248769388</v>
+        <v>-8.017332370542576</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-0.8083972699291034</v>
       </c>
       <c r="E97">
-        <v>-42.31544891742577</v>
+        <v>-42.64380403924794</v>
       </c>
       <c r="F97">
-        <v>-1.980561994683707</v>
+        <v>-2.285233040331157</v>
       </c>
       <c r="G97">
-        <v>-7.468462752964901</v>
+        <v>-7.942845359921621</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-0.7303341479932935</v>
       </c>
       <c r="E98">
-        <v>-43.74911850351413</v>
+        <v>-44.35319202953031</v>
       </c>
       <c r="F98">
-        <v>-1.860363399435291</v>
+        <v>-1.921695721938566</v>
       </c>
       <c r="G98">
-        <v>-8.437115450750134</v>
+        <v>-7.691126447988819</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-0.6424845766092585</v>
       </c>
       <c r="E99">
-        <v>-45.76180783317123</v>
+        <v>-46.48954039891487</v>
       </c>
       <c r="F99">
-        <v>-2.12222690280827</v>
+        <v>-2.446194767103935</v>
       </c>
       <c r="G99">
-        <v>-8.437053107540505</v>
+        <v>-7.84812961838669</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-0.549188277428716</v>
       </c>
       <c r="E100">
-        <v>-47.87421868895125</v>
+        <v>-47.89749730958768</v>
       </c>
       <c r="F100">
-        <v>-2.002398587788905</v>
+        <v>-2.634696396550185</v>
       </c>
       <c r="G100">
-        <v>-9.085360144477152</v>
+        <v>-9.136583294241643</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-0.4566421823628218</v>
       </c>
       <c r="E101">
-        <v>-49.72264554880962</v>
+        <v>-50.36108453195152</v>
       </c>
       <c r="F101">
-        <v>-1.97662145094859</v>
+        <v>-3.018519604269933</v>
       </c>
       <c r="G101">
-        <v>-8.860005847774488</v>
+        <v>-9.30459496297145</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-0.3698761141405192</v>
       </c>
       <c r="E102">
-        <v>-51.6399652158652</v>
+        <v>-52.41409992264693</v>
       </c>
       <c r="F102">
-        <v>-2.105889012522856</v>
+        <v>-3.15126133873154</v>
       </c>
       <c r="G102">
-        <v>-9.385050515609034</v>
+        <v>-10.18867089384044</v>
       </c>
     </row>
   </sheetData>
